--- a/artfynd/A 22382-2024 artfynd.xlsx
+++ b/artfynd/A 22382-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118763810</v>
+        <v>118763168</v>
       </c>
       <c r="B2" t="n">
         <v>97846</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509440</v>
+        <v>509384</v>
       </c>
       <c r="R2" t="n">
-        <v>6983457</v>
+        <v>6983606</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118763339</v>
+        <v>118762693</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509422</v>
+        <v>509286</v>
       </c>
       <c r="R3" t="n">
-        <v>6983592</v>
+        <v>6983652</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118763653</v>
+        <v>118763359</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -952,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509400</v>
+        <v>509433</v>
       </c>
       <c r="R4" t="n">
-        <v>6983527</v>
+        <v>6983578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118763531</v>
+        <v>118762551</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1073,12 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1087,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509412</v>
+        <v>509291</v>
       </c>
       <c r="R5" t="n">
-        <v>6983542</v>
+        <v>6983618</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1154,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118763678</v>
+        <v>118763531</v>
       </c>
       <c r="B6" t="n">
         <v>97846</v>
@@ -1194,7 +1189,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1208,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509397</v>
+        <v>509412</v>
       </c>
       <c r="R6" t="n">
-        <v>6983531</v>
+        <v>6983542</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1401,7 +1396,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118762551</v>
+        <v>118763382</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1436,7 +1431,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509291</v>
+        <v>509439</v>
       </c>
       <c r="R8" t="n">
-        <v>6983618</v>
+        <v>6983570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,7 +1517,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118762693</v>
+        <v>118763653</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509286</v>
+        <v>509400</v>
       </c>
       <c r="R9" t="n">
-        <v>6983652</v>
+        <v>6983527</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118763018</v>
+        <v>118763339</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509362</v>
+        <v>509422</v>
       </c>
       <c r="R10" t="n">
-        <v>6983629</v>
+        <v>6983592</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,7 +1759,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118763168</v>
+        <v>118762934</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509384</v>
+        <v>509334</v>
       </c>
       <c r="R11" t="n">
-        <v>6983606</v>
+        <v>6983603</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,7 +1880,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118763382</v>
+        <v>118763810</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509439</v>
+        <v>509440</v>
       </c>
       <c r="R12" t="n">
-        <v>6983570</v>
+        <v>6983457</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,7 +2001,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118763406</v>
+        <v>118763018</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509434</v>
+        <v>509362</v>
       </c>
       <c r="R13" t="n">
-        <v>6983548</v>
+        <v>6983629</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2122,7 +2122,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118763359</v>
+        <v>118763093</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509433</v>
+        <v>509373</v>
       </c>
       <c r="R14" t="n">
-        <v>6983578</v>
+        <v>6983614</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,7 +2243,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118762934</v>
+        <v>118763406</v>
       </c>
       <c r="B15" t="n">
         <v>97846</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509334</v>
+        <v>509434</v>
       </c>
       <c r="R15" t="n">
-        <v>6983603</v>
+        <v>6983548</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2364,7 +2364,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118763093</v>
+        <v>118763482</v>
       </c>
       <c r="B16" t="n">
         <v>97846</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509373</v>
+        <v>509436</v>
       </c>
       <c r="R16" t="n">
-        <v>6983614</v>
+        <v>6983561</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2485,7 +2485,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118763482</v>
+        <v>118763678</v>
       </c>
       <c r="B17" t="n">
         <v>97846</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509436</v>
+        <v>509397</v>
       </c>
       <c r="R17" t="n">
-        <v>6983561</v>
+        <v>6983531</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2603,6 +2603,248 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118763101</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Månssonbäcken (Månssonbäcken), Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>509368</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6983610</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118762814</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Månssonbäcken (Månssonbäcken), Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>509281</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6983632</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22382-2024 artfynd.xlsx
+++ b/artfynd/A 22382-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118763168</v>
+        <v>118763810</v>
       </c>
       <c r="B2" t="n">
         <v>97846</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509384</v>
+        <v>509440</v>
       </c>
       <c r="R2" t="n">
-        <v>6983606</v>
+        <v>6983457</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118762693</v>
+        <v>118762551</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -831,12 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509286</v>
+        <v>509291</v>
       </c>
       <c r="R3" t="n">
-        <v>6983652</v>
+        <v>6983618</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118763359</v>
+        <v>118762693</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -966,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509433</v>
+        <v>509286</v>
       </c>
       <c r="R4" t="n">
-        <v>6983578</v>
+        <v>6983652</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1006,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1033,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118762551</v>
+        <v>118763482</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1073,7 +1068,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509291</v>
+        <v>509436</v>
       </c>
       <c r="R5" t="n">
-        <v>6983618</v>
+        <v>6983561</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118762982</v>
+        <v>118763168</v>
       </c>
       <c r="B7" t="n">
         <v>97846</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509349</v>
+        <v>509384</v>
       </c>
       <c r="R7" t="n">
-        <v>6983613</v>
+        <v>6983606</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,7 +1396,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118763382</v>
+        <v>118763678</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509439</v>
+        <v>509397</v>
       </c>
       <c r="R8" t="n">
-        <v>6983570</v>
+        <v>6983531</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,7 +1517,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118763653</v>
+        <v>118763359</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509400</v>
+        <v>509433</v>
       </c>
       <c r="R9" t="n">
-        <v>6983527</v>
+        <v>6983578</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118763339</v>
+        <v>118763093</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509422</v>
+        <v>509373</v>
       </c>
       <c r="R10" t="n">
-        <v>6983592</v>
+        <v>6983614</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,7 +1759,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118762934</v>
+        <v>118763382</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509334</v>
+        <v>509439</v>
       </c>
       <c r="R11" t="n">
-        <v>6983603</v>
+        <v>6983570</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,7 +1880,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118763810</v>
+        <v>118763406</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509440</v>
+        <v>509434</v>
       </c>
       <c r="R12" t="n">
-        <v>6983457</v>
+        <v>6983548</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,7 +2001,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118763018</v>
+        <v>118763653</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509362</v>
+        <v>509400</v>
       </c>
       <c r="R13" t="n">
-        <v>6983629</v>
+        <v>6983527</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2122,7 +2122,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118763093</v>
+        <v>118762982</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509373</v>
+        <v>509349</v>
       </c>
       <c r="R14" t="n">
-        <v>6983614</v>
+        <v>6983613</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,7 +2243,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118763406</v>
+        <v>118762934</v>
       </c>
       <c r="B15" t="n">
         <v>97846</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509434</v>
+        <v>509334</v>
       </c>
       <c r="R15" t="n">
-        <v>6983548</v>
+        <v>6983603</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2364,7 +2364,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118763482</v>
+        <v>118763018</v>
       </c>
       <c r="B16" t="n">
         <v>97846</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509436</v>
+        <v>509362</v>
       </c>
       <c r="R16" t="n">
-        <v>6983561</v>
+        <v>6983629</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2485,7 +2485,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118763678</v>
+        <v>118763339</v>
       </c>
       <c r="B17" t="n">
         <v>97846</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2534,13 +2534,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509397</v>
+        <v>509422</v>
       </c>
       <c r="R17" t="n">
-        <v>6983531</v>
+        <v>6983592</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 22382-2024 artfynd.xlsx
+++ b/artfynd/A 22382-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118763810</v>
+        <v>118763168</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509440</v>
+        <v>509384</v>
       </c>
       <c r="R2" t="n">
-        <v>6983457</v>
+        <v>6983606</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118762551</v>
+        <v>118762693</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,7 +831,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509291</v>
+        <v>509286</v>
       </c>
       <c r="R3" t="n">
-        <v>6983618</v>
+        <v>6983652</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118762693</v>
+        <v>118763810</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509286</v>
+        <v>509440</v>
       </c>
       <c r="R4" t="n">
-        <v>6983652</v>
+        <v>6983457</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118763482</v>
+        <v>118763678</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1068,7 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1082,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509436</v>
+        <v>509397</v>
       </c>
       <c r="R5" t="n">
-        <v>6983561</v>
+        <v>6983531</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118763531</v>
+        <v>118763339</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,7 +1194,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1203,13 +1208,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509412</v>
+        <v>509422</v>
       </c>
       <c r="R6" t="n">
-        <v>6983542</v>
+        <v>6983592</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118763168</v>
+        <v>118762551</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1310,12 +1315,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509384</v>
+        <v>509291</v>
       </c>
       <c r="R7" t="n">
-        <v>6983606</v>
+        <v>6983618</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118763678</v>
+        <v>118763093</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509397</v>
+        <v>509373</v>
       </c>
       <c r="R8" t="n">
-        <v>6983531</v>
+        <v>6983614</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118763359</v>
+        <v>118763018</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509433</v>
+        <v>509362</v>
       </c>
       <c r="R9" t="n">
-        <v>6983578</v>
+        <v>6983629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118763093</v>
+        <v>118763406</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509373</v>
+        <v>509434</v>
       </c>
       <c r="R10" t="n">
-        <v>6983614</v>
+        <v>6983548</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118763382</v>
+        <v>118763482</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509439</v>
+        <v>509436</v>
       </c>
       <c r="R11" t="n">
-        <v>6983570</v>
+        <v>6983561</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118763406</v>
+        <v>118763382</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509434</v>
+        <v>509439</v>
       </c>
       <c r="R12" t="n">
-        <v>6983548</v>
+        <v>6983570</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2004,7 +2004,7 @@
         <v>118763653</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118762982</v>
+        <v>118763359</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509349</v>
+        <v>509433</v>
       </c>
       <c r="R14" t="n">
-        <v>6983613</v>
+        <v>6983578</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118762934</v>
+        <v>118763531</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509334</v>
+        <v>509412</v>
       </c>
       <c r="R15" t="n">
-        <v>6983603</v>
+        <v>6983542</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2364,10 +2364,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118763018</v>
+        <v>118762934</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509362</v>
+        <v>509334</v>
       </c>
       <c r="R16" t="n">
-        <v>6983629</v>
+        <v>6983603</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2485,10 +2485,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118763339</v>
+        <v>118762982</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2534,13 +2534,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509422</v>
+        <v>509349</v>
       </c>
       <c r="R17" t="n">
-        <v>6983592</v>
+        <v>6983613</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2606,10 +2606,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118763101</v>
+        <v>118762814</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509368</v>
+        <v>509281</v>
       </c>
       <c r="R18" t="n">
-        <v>6983610</v>
+        <v>6983632</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2727,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118762814</v>
+        <v>118763101</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509281</v>
+        <v>509368</v>
       </c>
       <c r="R19" t="n">
-        <v>6983632</v>
+        <v>6983610</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 22382-2024 artfynd.xlsx
+++ b/artfynd/A 22382-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118763168</v>
+        <v>118763678</v>
       </c>
       <c r="B2" t="n">
         <v>97853</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509384</v>
+        <v>509397</v>
       </c>
       <c r="R2" t="n">
-        <v>6983606</v>
+        <v>6983531</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118762693</v>
+        <v>118763359</v>
       </c>
       <c r="B3" t="n">
         <v>97853</v>
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509286</v>
+        <v>509433</v>
       </c>
       <c r="R3" t="n">
-        <v>6983652</v>
+        <v>6983578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118763810</v>
+        <v>118763406</v>
       </c>
       <c r="B4" t="n">
         <v>97853</v>
@@ -952,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509440</v>
+        <v>509434</v>
       </c>
       <c r="R4" t="n">
-        <v>6983457</v>
+        <v>6983548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118763678</v>
+        <v>118763482</v>
       </c>
       <c r="B5" t="n">
         <v>97853</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509397</v>
+        <v>509436</v>
       </c>
       <c r="R5" t="n">
-        <v>6983531</v>
+        <v>6983561</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118763339</v>
+        <v>118762982</v>
       </c>
       <c r="B6" t="n">
         <v>97853</v>
@@ -1208,13 +1208,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509422</v>
+        <v>509349</v>
       </c>
       <c r="R6" t="n">
-        <v>6983592</v>
+        <v>6983613</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118762551</v>
+        <v>118763810</v>
       </c>
       <c r="B7" t="n">
         <v>97853</v>
@@ -1315,7 +1315,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1324,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509291</v>
+        <v>509440</v>
       </c>
       <c r="R7" t="n">
-        <v>6983618</v>
+        <v>6983457</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1364,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1374,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1517,7 +1522,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118763018</v>
+        <v>118763339</v>
       </c>
       <c r="B9" t="n">
         <v>97853</v>
@@ -1552,7 +1557,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1566,13 +1571,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509362</v>
+        <v>509422</v>
       </c>
       <c r="R9" t="n">
-        <v>6983629</v>
+        <v>6983592</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1601,7 +1606,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1616,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,7 +1643,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118763406</v>
+        <v>118762693</v>
       </c>
       <c r="B10" t="n">
         <v>97853</v>
@@ -1673,7 +1678,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1687,10 +1692,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509434</v>
+        <v>509286</v>
       </c>
       <c r="R10" t="n">
-        <v>6983548</v>
+        <v>6983652</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1722,7 +1727,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1732,7 +1737,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,7 +1764,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118763482</v>
+        <v>118762934</v>
       </c>
       <c r="B11" t="n">
         <v>97853</v>
@@ -1794,7 +1799,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1808,10 +1813,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509436</v>
+        <v>509334</v>
       </c>
       <c r="R11" t="n">
-        <v>6983561</v>
+        <v>6983603</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,7 +1848,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,7 +1858,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,7 +1885,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118763382</v>
+        <v>118763531</v>
       </c>
       <c r="B12" t="n">
         <v>97853</v>
@@ -1915,7 +1920,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1929,10 +1934,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509439</v>
+        <v>509412</v>
       </c>
       <c r="R12" t="n">
-        <v>6983570</v>
+        <v>6983542</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1964,7 +1969,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,7 +1979,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,7 +2006,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118763653</v>
+        <v>118763382</v>
       </c>
       <c r="B13" t="n">
         <v>97853</v>
@@ -2036,7 +2041,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2050,10 +2055,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509400</v>
+        <v>509439</v>
       </c>
       <c r="R13" t="n">
-        <v>6983527</v>
+        <v>6983570</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2085,7 +2090,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2095,7 +2100,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2122,7 +2127,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118763359</v>
+        <v>118763018</v>
       </c>
       <c r="B14" t="n">
         <v>97853</v>
@@ -2157,7 +2162,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2171,10 +2176,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509433</v>
+        <v>509362</v>
       </c>
       <c r="R14" t="n">
-        <v>6983578</v>
+        <v>6983629</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2206,7 +2211,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2216,7 +2221,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,7 +2248,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118763531</v>
+        <v>118762551</v>
       </c>
       <c r="B15" t="n">
         <v>97853</v>
@@ -2278,12 +2283,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509412</v>
+        <v>509291</v>
       </c>
       <c r="R15" t="n">
-        <v>6983542</v>
+        <v>6983618</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2364,7 +2364,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118762934</v>
+        <v>118763653</v>
       </c>
       <c r="B16" t="n">
         <v>97853</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509334</v>
+        <v>509400</v>
       </c>
       <c r="R16" t="n">
-        <v>6983603</v>
+        <v>6983527</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2485,7 +2485,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118762982</v>
+        <v>118763168</v>
       </c>
       <c r="B17" t="n">
         <v>97853</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509349</v>
+        <v>509384</v>
       </c>
       <c r="R17" t="n">
-        <v>6983613</v>
+        <v>6983606</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2606,7 +2606,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118762814</v>
+        <v>118763101</v>
       </c>
       <c r="B18" t="n">
         <v>97853</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509281</v>
+        <v>509368</v>
       </c>
       <c r="R18" t="n">
-        <v>6983632</v>
+        <v>6983610</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2727,7 +2727,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118763101</v>
+        <v>118762814</v>
       </c>
       <c r="B19" t="n">
         <v>97853</v>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509368</v>
+        <v>509281</v>
       </c>
       <c r="R19" t="n">
-        <v>6983610</v>
+        <v>6983632</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
